--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/elder_exile.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/elder_exile.xlsx
@@ -388,7 +388,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:L115"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.55" customWidth="1" style="13" min="1" max="1"/>
     <col width="19.85" customWidth="1" style="13" min="2" max="2"/>
@@ -502,11 +502,11 @@
 Though this village is far from the world of men, we are not free from trouble. If thou wouldst serve our purpose, we may turn a blind eye.</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Uma #race atravessa a barreira e entra em nossa vila...?
-Então, deve ser ideia daquele jovem. Keh keh keh... Entendo. Aquele ali realmente não tem mais utilidade para o bracelete. Até mesmo nosso grande pai o abandonou.
-Ainda assim, uma vila isolada como esta não está totalmente livre de problemas de vez em quando. Se provar ser útil para nós, talvez fechemos os olhos para isso.</t>
+      <c r="L8" s="13" t="inlineStr">
+        <is>
+          <t>Um #race atravessando a barreira e entrando nesta vila...?
+Então deve ter sido obra daquela jovem. Keh keh keh... Sim, a pulseira já não tem mais uso para ele. Até nosso mestre Itzpalt o deixou de lado.
+Embora esta vila esteja longe do mundo dos homens, não estamos livres de encrenca. Se servires ao nosso propósito, podemos fechar os olhos.</t>
         </is>
       </c>
     </row>
@@ -551,9 +551,9 @@
           <t>Tell me about Issizzle.</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Conte-me sobre Issizzle.</t>
+      <c r="L12" s="13" t="inlineStr">
+        <is>
+          <t>Fale-me de Issizzle.</t>
         </is>
       </c>
     </row>
@@ -586,9 +586,9 @@
           <t>Do you know of Issizzle?</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Você conhece Issizzle?</t>
+      <c r="L13" s="13" t="inlineStr">
+        <is>
+          <t>Sabe de Issizzle?</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
           <t>I found Duponne, but...</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L14" s="13" t="inlineStr">
         <is>
           <t>Encontrei Duponne, mas...</t>
         </is>
@@ -666,9 +666,9 @@
           <t>About the Great Horn of Minotaur...</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Sobre o Grande Chifre do Minotauro...</t>
+      <c r="L15" s="13" t="inlineStr">
+        <is>
+          <t>Sobre a Grande Chifre de Minotauro...</t>
         </is>
       </c>
     </row>
@@ -701,9 +701,9 @@
           <t>I brought back Duponne.</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Eu trouxe Duponne de volta.</t>
+      <c r="L16" s="13" t="inlineStr">
+        <is>
+          <t>Trago Duponne de volta.</t>
         </is>
       </c>
     </row>
@@ -736,9 +736,9 @@
           <t>I have slain Duponne.</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Eu matei Duponne.</t>
+      <c r="L17" s="13" t="inlineStr">
+        <is>
+          <t>Matei Duponne.</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
           <t>Duponne is gone forever.</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L18" s="13" t="inlineStr">
         <is>
           <t>Duponne se foi para sempre.</t>
         </is>
@@ -832,11 +832,11 @@
 A troublesome foe indeed. Not even among us is there one strong enough to oppose him. And if such a one did exist, he would still not stoop to the quarrels of the world. For an exile is bound solely to his own atonement.</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>A abominação das trevas, Issizzle. Keh keh keh... Quem aqui poderia alegar ignorância desse nome?
-Antes de aviltar sua alma com carne impura, ele era aclamado como o mago mais próximo dos deuses.
-Um inimigo problemático, de fato. Nem mesmo entre nós há alguém forte o suficiente para enfrentá-lo. E se tal pessoa existisse, ainda assim não se rebaixaria às querelas do mundo. Pois um exilado está ligado unicamente à sua própria expiação.</t>
+      <c r="L28" s="13" t="inlineStr">
+        <is>
+          <t>A abominação das trevas, Issizzle. Keh keh keh... Quem aqui poderia alegar desconhecer esse nome?
+Antes de rebaixar a alma com carne imunda, era saudado como o feiticeiro mais próximo dos deuses.
+Um inimigo problemático de verdade. Nem entre nós há alguém forte o bastante para enfrentá-lo. E se tal existisse, ainda assim não se rebaixaria às brigas do mundo. Pois um exilado se prende unicamente à própria expiação.</t>
         </is>
       </c>
     </row>
@@ -854,9 +854,9 @@
           <t>Keh keh keh... Yet wait, adventurer. There is one task most fitting for thee. Shouldst thou succeed, I shall grant thee knowledge—an ancient recipe passed down from of old. A secret craft that may forge a blade against Issizzle himself.</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Keh keh keh... Mas espera, aventureiro. Há uma tarefa bastante adequada para ti. Se tiveres sucesso, eu te concederei conhecimento—uma receita antiga, transmitida desde tempos remotos. Um segredo de fabricação que pode forjar uma lâmina contra o próprio Issizzle.</t>
+      <c r="L29" s="13" t="inlineStr">
+        <is>
+          <t>Keh keh keh... Espera, aventureiro. Há uma tarefa muito apropriada a ti. Se tiveres êxito, concederei conhecimento: uma receita antiga passada desde tempos idos. Uma arte secreta que pode forjar uma lâmina contra o próprio Issizzle.</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
         <is>
           <t>キキキ…さて、どこから話すべきか。
 この村の南東にルーリエという神殿があるのを、汝は知っているか？　神々が地上から去り、今はもう海の底に沈んだ哀しきルーリエ…その神殿で、我は暮らしていたのだ。かつて、まだ人間だった頃な。
-神殿には、どこからか迷い混んだ大食いトドの子が一匹いて、我になついていた。名はデュポンヌといい、愚かしいほど食い意地の張ったやつだったが…キキキ…あの鈍重で愛らしい獣に、我は奇妙なほど情を注いでいたものだ。</t>
+神殿には、どこからか迷い込んだ大食いトドの子が一匹いて、我になついていた。名はデュポンヌといい、愚かしいほど食い意地の張ったやつだったが…キキキ…あの鈍重で愛らしい獣に、我は奇妙なほど情を注いでいたものだ。</t>
         </is>
       </c>
       <c r="K30" s="20" t="inlineStr">
@@ -878,11 +878,11 @@
 A hungry sea-lion pup strayed within its halls. She clung to me, aye. Her name was Duponne. Foolish, greedy thing... keh keh keh... Yet I grew strangely fond of that slow, endearing beast.</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L30" s="13" t="inlineStr">
         <is>
           <t>Keh keh keh... Agora, por onde começar?
-Conheces o templo chamado Lurie, a sudeste desta vila? Quando os deuses deixaram este mundo, o santuário afundou sob o mar. Ali eu um dia habitei, nos dias em que ainda era mortal.
-Um filhote de leão-marinho faminto entrou em seus salões. Ela se agarrou a mim, sim. Seu nome era Duponne. Coisa tola, gananciosa... keh keh keh... No entanto, acabei me afeiçoando estranhamente àquela besta lenta e cativante.</t>
+Sabes do templo chamado Lurie, a sudeste desta vila? Quando os deuses partiram deste mundo, o santuário afundou sob o mar. Ali eu outrora morava, nos dias em que ainda era mortal.
+Um filhote de leão-marinho faminto se enfiou em seus salões. Ela se apegou a mim, sim. O nome dela era Duponne. Coisa tola, gulosa... keh keh keh... Mas me apeguei estranhamente àquela besta lenta e encantadora.</t>
         </is>
       </c>
     </row>
@@ -904,11 +904,11 @@
 Keh keh keh... I hear it clearly... the sorrowful cry of that child, forgotten in the deep sea.</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Com o tempo, eu morri, e pelos pecados da minha vida fui condenado a uma penitência eterna nesta vila. Isso foi há milhares de anos.
-Eras se passaram desde então, de fato. No entanto, estranhamente... mesmo agora, eu o sinto! A presença de Duponne, ainda viva!
-Keh keh keh... Eu a ouço claramente... o choro pesaroso daquela criança, esquecida nas profundezas do mar.</t>
+      <c r="L31" s="13" t="inlineStr">
+        <is>
+          <t>Com o tempo morri, e pelos pecados da minha vida fui atado a penitência infinita nesta vila. Isso foi há milhares de anos.
+Eras se passaram, de fato. Mas, estranhamente... ainda agora sinto! A presença de Duponne, ainda viva!
+Keh keh keh... Ouço com clareza... o choro triste daquela criança, esquecida no mar profundo.</t>
         </is>
       </c>
     </row>
@@ -928,10 +928,10 @@
 Whether she remains the sea-lion she once was, or hath become some dreadful monster, I cannot say. If she cannot be saved, then grant the poor beast eternal rest. That is my wish.</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Peço-te que tragas Duponne de sua prisão sob as ondas.
-Se ela ainda é o leão-marinho que um dia foi, ou se tornou algum monstro terrível, não posso dizer. Se não puder ser salva, então concede à pobre besta o descanso eterno. Esse é o meu desejo.</t>
+      <c r="L32" s="13" t="inlineStr">
+        <is>
+          <t>Peço-te: traz Duponne de volta da prisão dela sob as ondas.
+Se ela continua sendo o leão-marinho que era, ou se virou algum monstro terrível, não posso dizer. Se não puder ser salva, então concede à pobre besta o descanso eterno. Esse é meu desejo.</t>
         </is>
       </c>
     </row>
@@ -949,9 +949,9 @@
           <t>Keh keh keh... Still the same foolish child. To have the power to live for millennia, and yet dwell in such a ruin... keh keh keh...</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Keh keh keh... Ainda a mesma criança tola. Ter o poder de viver por milênios e ainda assim habitar tal ruína... keh keh keh...</t>
+      <c r="L33" s="13" t="inlineStr">
+        <is>
+          <t>Keh keh keh... Ainda a mesma criança tola. Ter o poder de viver por milênios e morar numa ruína dessas... keh keh keh...</t>
         </is>
       </c>
     </row>
@@ -999,11 +999,11 @@
 In any case, with such a vast form, thou couldst hardly drag her back here.</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>Duponne, transformada em um dragão...?
-Que estranho... Eu me lembro dela como nada além de um filhote de leão-marinho faminto. No entanto, memórias mortais se desvanecem rapidamente.
-De qualquer forma, com uma forma tão vasta, dificilmente poderias arrastá-la de volta até aqui.</t>
+      <c r="L41" s="13" t="inlineStr">
+        <is>
+          <t>Duponne, crescida num dragão...?
+Que bizarro... Lembro dela como nada além de um filhote de leão-marinho faminto. Mas memórias mortais desvanecem rápido.
+De qualquer forma, com uma forma tão vasta, mal poderias arrastá-la até aqui.</t>
         </is>
       </c>
     </row>
@@ -1074,11 +1074,11 @@
 ...Although, I seem to remember a herd of minotaurs dwelling south of Yowyn, keh keh keh...</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Se alguém usasse o antigo artefato conhecido como Orbe do Dragão, talvez Duponne pudesse ser dominada.
-Mas... keh keh keh... os ingredientes para forjar tal ferramenta são escassos nesta vila. Sim, o ingrediente raro chamado Grande Chifre do Minotauro.
-...Embora eu me lembre de uma manada de minotauros vivendo ao sul de Yowyn, keh keh keh...</t>
+      <c r="L50" s="13" t="inlineStr">
+        <is>
+          <t>Se alguém usasse o dispositivo antigo conhecido como Orbe do Dragão, quem sabe Duponne pudesse ser atada.
+Mas... keh keh keh... os ingredientes para fabricar tal ferramenta faltam nesta vila. Sim, o ingrediente raro chamado Grande Chifre de Minotauro.
+...Embora, parece-me lembrar de um rebanho de minotauros morando ao sul de Yowyn, keh keh keh...</t>
         </is>
       </c>
     </row>
@@ -1114,11 +1114,11 @@
 ...Its use? Surely an adventurer like thee needeth no lesson. Keh keh keh... aye, simply hold it, and cast it at the beast.</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Ah! Tu trazes o Grande Chifre do Minotauro!
+      <c r="L56" s="13" t="inlineStr">
+        <is>
+          <t>Ah! Carregas a Grande Chifre de Minotauro!
 Com este ingrediente, o orbe para trazer Duponne de volta pode ser forjado.
-...Seu uso? Certamente um aventureiro como tu não precisa de lições. Keh keh keh... sim, basta segurá-lo e lançá-lo contra a besta.</t>
+...O uso? Certamente um aventureiro como tu precisa de lição. Keh keh keh... sim, simplesmente segure-o e arremesse-o na fera.</t>
         </is>
       </c>
     </row>
@@ -1179,10 +1179,10 @@
 What kept her to the sunken ruins for ages beyond count... nay, to seek the answer now is folly. Keh keh keh... </t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>Duponne... Entendo. Se esse foi o teu julgamento, não direi mais nada.
-O que a manteve nas ruínas submersas por eras incontáveis... não, buscar a resposta agora é tolice. Keh keh keh...</t>
+      <c r="L66" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Duponne... Entendo. Se tal foi o teu julgamento, não direi mais nada.
+O que a manteve nas ruínas submersas por eras sem conta... não, buscar a resposta agora é tolice. Keh keh keh... </t>
         </is>
       </c>
     </row>
@@ -1200,9 +1200,9 @@
           <t xml:space="preserve">Keh keh keh... </t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>Keh keh keh...</t>
+      <c r="L67" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Keh keh keh... </t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="L68" s="13" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -1254,10 +1254,10 @@
 I shall grant thee a recipe of ancient sorcery—Rune Forging, a knowledge long lost to men. In thy battle with Issizzle, it shall surely serve thee well.</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>...Não te preocupes. Não abandonarei a promessa que te fiz.
-Eu te concederei uma receita de magia antiga—Forja de Runas, um conhecimento há muito perdido pelos homens. Em tua batalha contra Issizzle, ela certamente te servirá bem.</t>
+      <c r="L70" s="13" t="inlineStr">
+        <is>
+          <t>...Não temas. A promessa que fiz a ti não abandonarei.
+Concederei a ti uma receita de feitiçaria antiga: Forja de Runas, um conhecimento há muito perdido para os homens. Na tua batalha com Issizzle, certamente te servirá bem.</t>
         </is>
       </c>
     </row>
@@ -1275,9 +1275,9 @@
           <t>Our bargain is fulfilled. Now begone, adventurer. Keh keh keh...</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>Nosso acordo está cumprido. Agora suma daqui, aventureiro. Keh keh keh...</t>
+      <c r="L71" s="13" t="inlineStr">
+        <is>
+          <t>Nosso trato está cumprido. Agora vai, aventureiro. Keh keh keh...</t>
         </is>
       </c>
     </row>
@@ -1324,9 +1324,9 @@
           <t>...Duponne! Is it truly thee!?</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>...Duponne! És tu mesmo!?</t>
+      <c r="L78" s="13" t="inlineStr">
+        <is>
+          <t>...Duponne! É mesmo tu!?</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
           <t>GROOOOAAARRRR!!!</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="L80" s="13" t="inlineStr">
         <is>
           <t>GROOOOAAARRRR!!!</t>
         </is>
@@ -1385,9 +1385,9 @@
 Keh keh keh... Aye, I suppose thou rememberest me not.</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>Ah, que rugido pavoroso! Pretendes me devorar?
+      <c r="L81" s="13" t="inlineStr">
+        <is>
+          <t>Ah, que rugido medonho! Pretendes me devorar?
 Keh keh keh... Sim, suponho que não te lembras de mim.</t>
         </is>
       </c>
@@ -1425,7 +1425,7 @@
           <t>GROOOOAAAOOOONNNNN!!!</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="L83" s="13" t="inlineStr">
         <is>
           <t>GROOOOAAAOOOONNNNN!!!</t>
         </is>
@@ -1448,10 +1448,10 @@
 Still, to behold thee alive once more is enough for me. This withered life I do not prize. Do as thou wilt.</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>...Tu eras um dragão o tempo todo.
-Ainda assim, ver-te vivo mais uma vez é o bastante para mim. Esta vida desgastada não me importa. Faz o que quiseres.</t>
+      <c r="L84" s="13" t="inlineStr">
+        <is>
+          <t>...Tu eras um dragão desde sempre.
+Ainda assim, te ver viva mais uma vez basta para mim. Esta vida mirrada eu não aprecio. Faze o que quiseres.</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
           <t>GRRRRUUUUMMM... WHIIINE...</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="L87" s="13" t="inlineStr">
         <is>
           <t>GRRRRUUUUMMM... WHIIINE...</t>
         </is>
@@ -1505,7 +1505,7 @@
           <t>Duponne...?</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="L88" s="13" t="inlineStr">
         <is>
           <t>Duponne...?</t>
         </is>
@@ -1530,7 +1530,7 @@
           <t>WHIIINE... WHIIIIIINE...</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="L89" s="13" t="inlineStr">
         <is>
           <t>WHIIINE... WHIIIIIINE...</t>
         </is>
@@ -1555,11 +1555,11 @@
 And thou hast cherished it all these years...?</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>O quê, Duponne... será possível que te lembras de mim?
-Ah...! Aquele laço em teu pescoço! É o mesmo que eu amarrei em ti de brincadeira, há tanto, tanto tempo.
-E tu o guardaste todos esses anos...?</t>
+      <c r="L90" s="13" t="inlineStr">
+        <is>
+          <t>Que, Duponne... pode ser, te lembras de mim?
+Ah...! Aquela fita no teu pescoço! É a mesma que prendi em ti de brincadeira, há muito, muito tempo.
+E a guardaste todos estes anos...?</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1608,7 @@
           <t>WHIIINE... WHIMPER...</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
+      <c r="L95" s="13" t="inlineStr">
         <is>
           <t>WHIIINE... WHIMPER...</t>
         </is>
@@ -1630,10 +1630,10 @@
 I left thee in the ocean’s depths, bound myself to endless penance. Yet even after thousands of years, thou hast not forsaken me.</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>Duponne... então é verdade... então é verdade. Keh keh keh...
-Eu te deixei nas profundezas do oceano, me condenei a uma penitência sem fim. No entanto, mesmo após milhares de anos, tu não me abandonaste.</t>
+      <c r="L96" s="13" t="inlineStr">
+        <is>
+          <t>Duponne... é isso... é isso. Keh keh keh...
+Deixei-te nas profundezas do oceano, atando-me a penitência infinita. Mas mesmo depois de milhares de anos, não me abandonaste.</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
           <t xml:space="preserve">WHIMPER... </t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
+      <c r="L97" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">WHIMPER... </t>
         </is>
@@ -1676,9 +1676,9 @@
           <t>Forgive me, Duponne... Forgive this foolish soul of mine.</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>Perdoa-me, Duponne... Perdoa esta alma tola.</t>
+      <c r="L98" s="13" t="inlineStr">
+        <is>
+          <t>Perdoa-me, Duponne... Perdoa esta alma tola que sou.</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
           <t>WHIIIINE... GROOOOANNN...!</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
+      <c r="L100" s="13" t="inlineStr">
         <is>
           <t>WHIIIINE... GROOOOANNN...!</t>
         </is>
@@ -1735,7 +1735,7 @@
           <t>Oh, Duponne...!</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
+      <c r="L101" s="13" t="inlineStr">
         <is>
           <t>Oh, Duponne...!</t>
         </is>
@@ -1760,7 +1760,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
+      <c r="L102" s="13" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -1780,7 +1780,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
+      <c r="L103" s="13" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -1815,10 +1815,10 @@
 I shall grant thee a recipe of ancient sorcery—Rune Forging, a knowledge long lost to men. In thy battle with Issizzle, it shall surely serve thee well.</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>Keh keh keh... Não te preocupes. A promessa que te fiz não será quebrada.
-Vou te conceder uma receita de magia ancestral—Forja de Runas, um conhecimento há muito perdido pelos homens. Em tua batalha contra Issizzle, ela certamente te será útil.</t>
+      <c r="L105" s="13" t="inlineStr">
+        <is>
+          <t>Keh keh keh... Não temas. A promessa que fiz a ti não abandonarei.
+Concederei a ti uma receita de feitiçaria antiga: Forja de Runas, um conhecimento há muito perdido para os homens. Na tua batalha com Issizzle, certamente te servirá bem.</t>
         </is>
       </c>
     </row>
@@ -1844,11 +1844,11 @@
 Come now, Duponne, come hither. Let us live together once more... as we did in those days at Lurie. Keh keh keh...</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>Agora então, Duponne, devemos te apresentar aos aldeões!
-Keh keh keh... Não temas. Seus rostos são severos, mas não te farão mal. Creio que te tornarás um dos favoritos entre eles.
-Vem agora, Duponne, vem aqui. Vamos viver juntos mais uma vez... como fazíamos naqueles dias em Lurie. Keh keh keh...</t>
+      <c r="L107" s="13" t="inlineStr">
+        <is>
+          <t>Agora, Duponne, temos de te mostrar ao povo da vila!
+Keh keh keh... Não temas. As caras deles são sérias, mas não querem te machucar. Virarás a preferida deles, acho.
+Vem, Duponne, vem cá. Vamos viver juntos mais uma vez... como naqueles dias em Lurie. Keh keh keh...</t>
         </is>
       </c>
     </row>
@@ -1898,11 +1898,11 @@
 Forget this not. The one thou wouldst face dwelleth in a realm far beyond the petty quarrels of earth. Thou standest now with thy hand upon the very gates of myth. Keh keh keh...</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>Quando Issizle ainda era um homem, reis e nobres dobravam os joelhos para implorar por sua ajuda. Keh keh keh... Com o poder que ele empunhava, subjugar os reinos da terra teria sido mero capricho.
-No entanto, ele ainda permanece em seu castelo em ruínas, perdido em estudos intermináveis das pedras mágicas. Pois, aos seus olhos, as coroas e glórias da humanidade não passam de pó.
-Não esqueças isso. Aquele a quem enfrentarias habita um reino muito além das mesquinhas querelas terrenas. Agora, estás com a mão sobre os próprios portões do mito. Keh keh keh...</t>
+      <c r="L113" s="13" t="inlineStr">
+        <is>
+          <t>Quando Issizle ainda era homem, reis e nobres dobravam os joelhos implorando sua ajuda. Keh keh keh... Com o poder que ele empunhava, subjugar os reinos da terra seria banal.
+Mas ele ainda mora em seu castelo em ruínas, perdido no estudo infinito das pedras mágicas. Pois aos olhos dele, as coroas e glórias da humanidade são pó.
+Não esqueças isto. Aquele que enfrentas mora num reino muito além das brigas mesquinhas da terra. Estás agora com a mão nos portões do mito. Keh keh keh...</t>
         </is>
       </c>
     </row>
